--- a/data.xlsx
+++ b/data.xlsx
@@ -5,27 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\PythonProject\PythonProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bot\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C936047-DCD2-4E41-91D4-F4B34656EBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC8FB93-50E0-4068-B351-00FF0C44D804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Unit</t>
   </si>
@@ -36,7 +47,16 @@
     <t>CivilCharge</t>
   </si>
   <si>
-    <t>CardNumber</t>
+    <t>monthCurrent</t>
+  </si>
+  <si>
+    <t>monthCivil</t>
+  </si>
+  <si>
+    <t>آبان</t>
+  </si>
+  <si>
+    <t>مهر</t>
   </si>
 </sst>
 </file>
@@ -354,14 +374,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -371,64 +391,1117 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>102345</v>
+        <v>41904001</v>
       </c>
       <c r="C2">
-        <v>3490000</v>
-      </c>
-      <c r="D2">
-        <v>6037998149471380</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8526001</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2345612</v>
+        <v>39132002</v>
       </c>
       <c r="C3">
-        <v>34568765</v>
-      </c>
-      <c r="D3">
-        <v>6037998149471380</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>31732002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>120045673</v>
+        <v>41059003</v>
       </c>
       <c r="C4">
-        <v>237654</v>
-      </c>
-      <c r="D4">
-        <v>6037998149471380</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7799003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>127834</v>
+        <v>42244004</v>
       </c>
       <c r="C5">
-        <v>1263000</v>
-      </c>
-      <c r="D5">
-        <v>6037998149471380</v>
+        <v>4448004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>45289005</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>18017006</v>
+      </c>
+      <c r="C7">
+        <v>7623006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>42214007</v>
+      </c>
+      <c r="C8">
+        <v>13291007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>75120008</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>45497009</v>
+      </c>
+      <c r="C10">
+        <v>4422009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>50671010</v>
+      </c>
+      <c r="C11">
+        <v>6394010</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>49288012</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>47697013</v>
+      </c>
+      <c r="C14">
+        <v>11220013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>40744014</v>
+      </c>
+      <c r="C15">
+        <v>7273014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>42451015</v>
+      </c>
+      <c r="C16">
+        <v>3357015</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>40218016</v>
+      </c>
+      <c r="C17">
+        <v>5338016</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>46199017</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>42339018</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>40792019</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>49206020</v>
+      </c>
+      <c r="C21">
+        <v>12231020</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>40255021</v>
+      </c>
+      <c r="C22">
+        <v>8459021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>44640022</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>41058023</v>
+      </c>
+      <c r="C24">
+        <v>3806023</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>40595024</v>
+      </c>
+      <c r="C25">
+        <v>8893024</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>40220025</v>
+      </c>
+      <c r="C26">
+        <v>4245025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>39420026</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>66637027</v>
+      </c>
+      <c r="C28">
+        <v>6482027</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>89505028</v>
+      </c>
+      <c r="C29">
+        <v>9008028</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>42199029</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>50700030</v>
+      </c>
+      <c r="C31">
+        <v>7240030</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>50767031</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>49288032</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>46049033</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>42393034</v>
+      </c>
+      <c r="C35">
+        <v>10910034</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>40802035</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>43906036</v>
+      </c>
+      <c r="C37">
+        <v>5344036</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>44550037</v>
+      </c>
+      <c r="C38">
+        <v>11384037</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>39022038</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>40792039</v>
+      </c>
+      <c r="C40">
+        <v>3663039</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>46056040</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>40255041</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>40793042</v>
+      </c>
+      <c r="C43">
+        <v>10988042</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>40211043</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>39892044</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>40220045</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>41068046</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>40918047</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>68952048</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>42176049</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>50700050</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>50715051</v>
+      </c>
+      <c r="C52">
+        <v>7243051</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>50938052</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>47603053</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>39095054</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>42451055</v>
+      </c>
+      <c r="C56">
+        <v>7336055</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>43820056</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>43632057</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>40734058</v>
+      </c>
+      <c r="C59">
+        <v>7195058</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>40792059</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>44479060</v>
+      </c>
+      <c r="C61">
+        <v>5568060</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>41905061</v>
+      </c>
+      <c r="C62">
+        <v>8526061</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>42441062</v>
+      </c>
+      <c r="C63">
+        <v>3663062</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>41058063</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>42244064</v>
+      </c>
+      <c r="C65">
+        <v>4429064</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>39458065</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>41069066</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>45866067</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>42363068</v>
+      </c>
+      <c r="C69">
+        <v>4511068</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>42214069</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>47401070</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>47438071</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>52586072</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>46035073</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>5982075</v>
+      </c>
+      <c r="C76">
+        <v>10964075</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>42253076</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>44550077</v>
+      </c>
+      <c r="C78">
+        <v>78295077</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>39022078</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>40792079</v>
+      </c>
+      <c r="C80">
+        <v>6847079</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>46057080</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>43553081</v>
+      </c>
+      <c r="C82">
+        <v>8495081</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>40717082</v>
+      </c>
+      <c r="C83">
+        <v>3520082</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>39409083</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>42244084</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>41869085</v>
+      </c>
+      <c r="C86">
+        <v>8489085</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>41069086</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>44119087</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>44012088</v>
+      </c>
+      <c r="C89">
+        <v>9022088</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>42199089</v>
+      </c>
+      <c r="C90">
+        <v>13266089</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>44103090</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>52407091</v>
+      </c>
+      <c r="C92">
+        <v>7240091</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>50933092</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>46048093</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>39095094</v>
+      </c>
+      <c r="C95">
+        <v>7068094</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>45741095</v>
+      </c>
+      <c r="C96">
+        <v>3725095</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>36913096</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>41251097</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>39022098</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>40792099</v>
+      </c>
+      <c r="C100">
+        <v>7325099</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>41108100</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bot\version 2\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC8FB93-50E0-4068-B351-00FF0C44D804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>Unit</t>
   </si>
@@ -53,16 +47,13 @@
     <t>monthCivil</t>
   </si>
   <si>
-    <t>آبان</t>
-  </si>
-  <si>
     <t>مهر</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -366,22 +357,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -398,7 +389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -412,10 +403,10 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -426,7 +417,7 @@
         <v>31732002</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -437,7 +428,7 @@
         <v>7799003</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -448,7 +439,7 @@
         <v>4448004</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -459,7 +450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -470,7 +461,7 @@
         <v>7623006</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -481,7 +472,7 @@
         <v>13291007</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -492,7 +483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -503,7 +494,7 @@
         <v>4422009</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -514,7 +505,7 @@
         <v>6394010</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -525,7 +516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -536,7 +527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -547,7 +538,7 @@
         <v>11220013</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -558,7 +549,7 @@
         <v>7273014</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -569,7 +560,7 @@
         <v>3357015</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -580,7 +571,7 @@
         <v>5338016</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -591,7 +582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -602,7 +593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -613,7 +604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -624,7 +615,7 @@
         <v>12231020</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -635,7 +626,7 @@
         <v>8459021</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -646,7 +637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -657,7 +648,7 @@
         <v>3806023</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -668,7 +659,7 @@
         <v>8893024</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -679,7 +670,7 @@
         <v>4245025</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -690,7 +681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -701,7 +692,7 @@
         <v>6482027</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -712,7 +703,7 @@
         <v>9008028</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -723,7 +714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -734,7 +725,7 @@
         <v>7240030</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -745,7 +736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -756,7 +747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -767,7 +758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -778,7 +769,7 @@
         <v>10910034</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -789,7 +780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -800,7 +791,7 @@
         <v>5344036</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -811,7 +802,7 @@
         <v>11384037</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -822,7 +813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -833,7 +824,7 @@
         <v>3663039</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -844,7 +835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -855,7 +846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -866,7 +857,7 @@
         <v>10988042</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -877,7 +868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -888,7 +879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -899,7 +890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -910,7 +901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -921,7 +912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -932,7 +923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -943,7 +934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -954,7 +945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -965,7 +956,7 @@
         <v>7243051</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -976,7 +967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -987,7 +978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -998,7 +989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1009,7 +1000,7 @@
         <v>7336055</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1020,7 +1011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1031,7 +1022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1042,7 +1033,7 @@
         <v>7195058</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1053,7 +1044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1064,7 +1055,7 @@
         <v>5568060</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1075,7 +1066,7 @@
         <v>8526061</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1086,7 +1077,7 @@
         <v>3663062</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1097,7 +1088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1108,7 +1099,7 @@
         <v>4429064</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1119,7 +1110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1130,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1141,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1152,7 +1143,7 @@
         <v>4511068</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1163,7 +1154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1174,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1185,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1196,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1207,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1218,7 +1209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1229,7 +1220,7 @@
         <v>10964075</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1240,7 +1231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1251,7 +1242,7 @@
         <v>78295077</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1262,7 +1253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1273,7 +1264,7 @@
         <v>6847079</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1284,7 +1275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1295,7 +1286,7 @@
         <v>8495081</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1306,7 +1297,7 @@
         <v>3520082</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1317,7 +1308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1328,7 +1319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1339,7 +1330,7 @@
         <v>8489085</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1350,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1361,7 +1352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1372,7 +1363,7 @@
         <v>9022088</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1383,7 +1374,7 @@
         <v>13266089</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1394,7 +1385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1405,7 +1396,7 @@
         <v>7240091</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1416,7 +1407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1427,7 +1418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1438,7 +1429,7 @@
         <v>7068094</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1449,7 +1440,7 @@
         <v>3725095</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1460,7 +1451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1471,7 +1462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1482,7 +1473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1493,7 +1484,7 @@
         <v>7325099</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,31 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\charges\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8344020F-5443-4566-82B8-B7CA343CA0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -53,7 +43,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -83,8 +73,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,22 +348,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -389,14 +381,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>41904001</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>8526001</v>
       </c>
       <c r="F2" t="s">
@@ -406,1092 +398,1092 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>39132002</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>31732002</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>41059003</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>7799003</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>42244004</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>4448004</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>45289005</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>18017006</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>7623006</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>42214007</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>13291007</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>75120008</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>45497009</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>4422009</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>50671010</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>6394010</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>49288012</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>47697013</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>11220013</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>40744014</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>7273014</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>42451015</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>3357015</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>40218016</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>5338016</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>46199017</v>
       </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>42339018</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>40792019</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>49206020</v>
       </c>
-      <c r="C21">
-        <v>12231020</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>40255021</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>8459021</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>44640022</v>
       </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>41058023</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>3806023</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>40595024</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>8893024</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26">
-        <v>40220025</v>
-      </c>
-      <c r="C26">
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
         <v>4245025</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>39420026</v>
       </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>66637027</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>6482027</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>89505028</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>9008028</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>42199029</v>
       </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>50700030</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>7240030</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>50767031</v>
       </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>49288032</v>
       </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="1">
         <v>46049033</v>
       </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="1">
         <v>42393034</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="1">
         <v>10910034</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="1">
         <v>40802035</v>
       </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="1">
         <v>43906036</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="1">
         <v>5344036</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="1">
         <v>44550037</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="1">
         <v>11384037</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="1">
         <v>39022038</v>
       </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="1">
         <v>40792039</v>
       </c>
-      <c r="C40">
-        <v>3663039</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="1">
         <v>46056040</v>
       </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="1">
         <v>40255041</v>
       </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="1">
         <v>40793042</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="1">
         <v>10988042</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="1">
         <v>40211043</v>
       </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="1">
         <v>39892044</v>
       </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="1">
         <v>40220045</v>
       </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="1">
         <v>41068046</v>
       </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="1">
         <v>40918047</v>
       </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="1">
         <v>68952048</v>
       </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="1">
         <v>42176049</v>
       </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="1">
         <v>50700050</v>
       </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="1">
         <v>50715051</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="1">
         <v>7243051</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="1">
         <v>50938052</v>
       </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="1">
         <v>47603053</v>
       </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="1">
         <v>39095054</v>
       </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="1">
         <v>42451055</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="1">
         <v>7336055</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="1">
         <v>43820056</v>
       </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="1">
         <v>43632057</v>
       </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="1">
         <v>40734058</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="1">
         <v>7195058</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="1">
         <v>40792059</v>
       </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="1">
         <v>44479060</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="1">
         <v>5568060</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62">
-        <v>41905061</v>
-      </c>
-      <c r="C62">
+      <c r="B62" s="1">
+        <v>0</v>
+      </c>
+      <c r="C62" s="1">
         <v>8526061</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="1">
         <v>42441062</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="1">
         <v>3663062</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="1">
         <v>41058063</v>
       </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="1">
         <v>42244064</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="1">
         <v>4429064</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="1">
         <v>39458065</v>
       </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="1">
         <v>41069066</v>
       </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="1">
         <v>45866067</v>
       </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="1">
         <v>42363068</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="1">
         <v>4511068</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="1">
         <v>42214069</v>
       </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71">
-        <v>47401070</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="1">
+        <v>0</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="1">
         <v>47438071</v>
       </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="1">
         <v>52586072</v>
       </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74">
-        <v>46035073</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="1">
+        <v>0</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="1">
+        <v>0</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="1">
         <v>5982075</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="1">
         <v>10964075</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="1">
         <v>42253076</v>
       </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="1">
         <v>44550077</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="1">
         <v>78295077</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="1">
         <v>39022078</v>
       </c>
-      <c r="C79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="1">
         <v>40792079</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="1">
         <v>6847079</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="1">
         <v>46057080</v>
       </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="1">
         <v>43553081</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="1">
         <v>8495081</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="1">
         <v>40717082</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="1">
         <v>3520082</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="1">
         <v>39409083</v>
       </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="1">
         <v>42244084</v>
       </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="1">
         <v>41869085</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="1">
         <v>8489085</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="1">
         <v>41069086</v>
       </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="1">
         <v>44119087</v>
       </c>
-      <c r="C88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="1">
         <v>44012088</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="1">
         <v>9022088</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="1">
         <v>42199089</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="1">
         <v>13266089</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="1">
         <v>44103090</v>
       </c>
-      <c r="C91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="1">
         <v>52407091</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="1">
         <v>7240091</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="1">
         <v>50933092</v>
       </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="1">
         <v>46048093</v>
       </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C94" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="1">
         <v>39095094</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="1">
         <v>7068094</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="1">
         <v>45741095</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="1">
         <v>3725095</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97">
-        <v>36913096</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B97" s="1">
+        <v>0</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="1">
         <v>41251097</v>
       </c>
-      <c r="C98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="1">
         <v>39022098</v>
       </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="1">
         <v>40792099</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="1">
         <v>7325099</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="1">
         <v>41108100</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\charges\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8344020F-5443-4566-82B8-B7CA343CA0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13A977C-E047-429D-B485-6B7C3AFF6A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Unit</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>مهر</t>
+  </si>
+  <si>
+    <t>آبان</t>
   </si>
 </sst>
 </file>
@@ -389,13 +392,13 @@
         <v>41904001</v>
       </c>
       <c r="C2" s="1">
-        <v>8526001</v>
+        <v>20706001</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -406,7 +409,7 @@
         <v>39132002</v>
       </c>
       <c r="C3" s="1">
-        <v>31732002</v>
+        <v>42196002</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -417,7 +420,7 @@
         <v>41059003</v>
       </c>
       <c r="C4" s="1">
-        <v>7799003</v>
+        <v>18673003</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -428,7 +431,7 @@
         <v>42244004</v>
       </c>
       <c r="C5" s="1">
-        <v>4448004</v>
+        <v>17152004</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -450,7 +453,7 @@
         <v>18017006</v>
       </c>
       <c r="C7" s="1">
-        <v>7623006</v>
+        <v>18513006</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -461,7 +464,7 @@
         <v>42214007</v>
       </c>
       <c r="C8" s="1">
-        <v>13291007</v>
+        <v>25949007</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -472,7 +475,7 @@
         <v>75120008</v>
       </c>
       <c r="C9" s="1">
-        <v>0</v>
+        <v>13391008</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -483,7 +486,7 @@
         <v>45497009</v>
       </c>
       <c r="C10" s="1">
-        <v>4422009</v>
+        <v>17056009</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -494,7 +497,7 @@
         <v>50671010</v>
       </c>
       <c r="C11" s="1">
-        <v>6394010</v>
+        <v>24660010</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -505,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="1">
-        <v>0</v>
+        <v>17682011</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -513,10 +516,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>49288012</v>
+        <v>0</v>
       </c>
       <c r="C13" s="1">
-        <v>0</v>
+        <v>23568012</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -527,7 +530,7 @@
         <v>47697013</v>
       </c>
       <c r="C14" s="1">
-        <v>11220013</v>
+        <v>27248013</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -538,7 +541,7 @@
         <v>40744014</v>
       </c>
       <c r="C15" s="1">
-        <v>7273014</v>
+        <v>17663014</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -549,7 +552,7 @@
         <v>42451015</v>
       </c>
       <c r="C16" s="1">
-        <v>3357015</v>
+        <v>10480015</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -560,7 +563,7 @@
         <v>40218016</v>
       </c>
       <c r="C17" s="1">
-        <v>5338016</v>
+        <v>20606016</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -568,10 +571,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>46199017</v>
+        <v>0</v>
       </c>
       <c r="C18" s="1">
-        <v>0</v>
+        <v>16262017</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -579,7 +582,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>42339018</v>
+        <v>0</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -593,7 +596,7 @@
         <v>40792019</v>
       </c>
       <c r="C20" s="1">
-        <v>0</v>
+        <v>10465019</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -604,7 +607,7 @@
         <v>49206020</v>
       </c>
       <c r="C21" s="1">
-        <v>0</v>
+        <v>8271020</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -615,7 +618,7 @@
         <v>40255021</v>
       </c>
       <c r="C22" s="1">
-        <v>8459021</v>
+        <v>20639021</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -626,7 +629,7 @@
         <v>44640022</v>
       </c>
       <c r="C23" s="1">
-        <v>0</v>
+        <v>10648022</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -637,7 +640,7 @@
         <v>41058023</v>
       </c>
       <c r="C24" s="1">
-        <v>3806023</v>
+        <v>14680023</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -648,7 +651,7 @@
         <v>40595024</v>
       </c>
       <c r="C25" s="1">
-        <v>8893024</v>
+        <v>21597024</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -659,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="1">
-        <v>4245025</v>
+        <v>16371025</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -667,10 +670,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>39420026</v>
+        <v>0</v>
       </c>
       <c r="C27" s="1">
-        <v>0</v>
+        <v>10892026</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -681,7 +684,7 @@
         <v>66637027</v>
       </c>
       <c r="C28" s="1">
-        <v>6482027</v>
+        <v>17140027</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -692,7 +695,7 @@
         <v>89505028</v>
       </c>
       <c r="C29" s="1">
-        <v>9008028</v>
+        <v>21896028</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -700,10 +703,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>42199029</v>
+        <v>0</v>
       </c>
       <c r="C30" s="1">
-        <v>0</v>
+        <v>8213029</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -714,7 +717,7 @@
         <v>50700030</v>
       </c>
       <c r="C31" s="1">
-        <v>7240030</v>
+        <v>27900030</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -725,7 +728,7 @@
         <v>50767031</v>
       </c>
       <c r="C32" s="1">
-        <v>0</v>
+        <v>20764031</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -733,10 +736,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>49288032</v>
+        <v>0</v>
       </c>
       <c r="C33" s="1">
-        <v>0</v>
+        <v>23570032</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -747,7 +750,7 @@
         <v>46049033</v>
       </c>
       <c r="C34" s="1">
-        <v>0</v>
+        <v>15928033</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -758,7 +761,7 @@
         <v>42393034</v>
       </c>
       <c r="C35" s="1">
-        <v>10910034</v>
+        <v>21300034</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -766,10 +769,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="1">
-        <v>40802035</v>
+        <v>0</v>
       </c>
       <c r="C36" s="1">
-        <v>0</v>
+        <v>10481035</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -780,7 +783,7 @@
         <v>43906036</v>
       </c>
       <c r="C37" s="1">
-        <v>5344036</v>
+        <v>20612036</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -791,7 +794,7 @@
         <v>44550037</v>
       </c>
       <c r="C38" s="1">
-        <v>11384037</v>
+        <v>27646037</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -802,7 +805,7 @@
         <v>39022038</v>
       </c>
       <c r="C39" s="1">
-        <v>0</v>
+        <v>10279038</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -813,7 +816,7 @@
         <v>40792039</v>
       </c>
       <c r="C40" s="1">
-        <v>0</v>
+        <v>10464039</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -824,7 +827,7 @@
         <v>46056040</v>
       </c>
       <c r="C41" s="1">
-        <v>0</v>
+        <v>16040040</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -835,7 +838,7 @@
         <v>40255041</v>
       </c>
       <c r="C42" s="1">
-        <v>0</v>
+        <v>12180041</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -846,7 +849,7 @@
         <v>40793042</v>
       </c>
       <c r="C43" s="1">
-        <v>10988042</v>
+        <v>21452042</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -857,7 +860,7 @@
         <v>40211043</v>
       </c>
       <c r="C44" s="1">
-        <v>0</v>
+        <v>10874043</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -868,7 +871,7 @@
         <v>39892044</v>
       </c>
       <c r="C45" s="1">
-        <v>0</v>
+        <v>12584044</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -879,7 +882,7 @@
         <v>40220045</v>
       </c>
       <c r="C46" s="1">
-        <v>0</v>
+        <v>12125045</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -890,7 +893,7 @@
         <v>41068046</v>
       </c>
       <c r="C47" s="1">
-        <v>0</v>
+        <v>10891046</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -901,7 +904,7 @@
         <v>40918047</v>
       </c>
       <c r="C48" s="1">
-        <v>0</v>
+        <v>10658047</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -909,7 +912,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1">
-        <v>68952048</v>
+        <v>62057048</v>
       </c>
       <c r="C49" s="1">
         <v>0</v>
@@ -920,10 +923,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="1">
-        <v>42176049</v>
+        <v>0</v>
       </c>
       <c r="C50" s="1">
-        <v>0</v>
+        <v>12634049</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -931,10 +934,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="1">
-        <v>50700050</v>
+        <v>0</v>
       </c>
       <c r="C51" s="1">
-        <v>0</v>
+        <v>20660050</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -942,10 +945,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="1">
-        <v>50715051</v>
+        <v>0</v>
       </c>
       <c r="C52" s="1">
-        <v>7243051</v>
+        <v>20727051</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -953,10 +956,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="1">
-        <v>50938052</v>
+        <v>0</v>
       </c>
       <c r="C53" s="1">
-        <v>0</v>
+        <v>23570052</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -967,7 +970,7 @@
         <v>47603053</v>
       </c>
       <c r="C54" s="1">
-        <v>0</v>
+        <v>15838053</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -975,10 +978,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="1">
-        <v>39095054</v>
+        <v>0</v>
       </c>
       <c r="C55" s="1">
-        <v>0</v>
+        <v>10388054</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -989,7 +992,7 @@
         <v>42451055</v>
       </c>
       <c r="C56" s="1">
-        <v>7336055</v>
+        <v>17816055</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -1000,7 +1003,7 @@
         <v>43820056</v>
       </c>
       <c r="C57" s="1">
-        <v>0</v>
+        <v>15253056</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -1011,7 +1014,7 @@
         <v>43632057</v>
       </c>
       <c r="C58" s="1">
-        <v>0</v>
+        <v>16287057</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1022,7 +1025,7 @@
         <v>40734058</v>
       </c>
       <c r="C59" s="1">
-        <v>7195058</v>
+        <v>17473058</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -1033,7 +1036,7 @@
         <v>40792059</v>
       </c>
       <c r="C60" s="1">
-        <v>0</v>
+        <v>10465059</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -1041,10 +1044,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="1">
-        <v>44479060</v>
+        <v>0</v>
       </c>
       <c r="C61" s="1">
-        <v>5568060</v>
+        <v>16040060</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1055,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="1">
-        <v>8526061</v>
+        <v>20706061</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1063,10 +1066,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="1">
-        <v>42441062</v>
+        <v>0</v>
       </c>
       <c r="C63" s="1">
-        <v>3663062</v>
+        <v>10464062</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -1077,7 +1080,7 @@
         <v>41058063</v>
       </c>
       <c r="C64" s="1">
-        <v>0</v>
+        <v>10875063</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -1088,7 +1091,7 @@
         <v>42244064</v>
       </c>
       <c r="C65" s="1">
-        <v>4429064</v>
+        <v>17133064</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -1096,7 +1099,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="1">
-        <v>39458065</v>
+        <v>0</v>
       </c>
       <c r="C66" s="1">
         <v>0</v>
@@ -1110,7 +1113,7 @@
         <v>41069066</v>
       </c>
       <c r="C67" s="1">
-        <v>0</v>
+        <v>10891066</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1118,10 +1121,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="1">
-        <v>45866067</v>
+        <v>0</v>
       </c>
       <c r="C68" s="1">
-        <v>0</v>
+        <v>10658067</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -1132,7 +1135,7 @@
         <v>42363068</v>
       </c>
       <c r="C69" s="1">
-        <v>4511068</v>
+        <v>17399068</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1143,7 +1146,7 @@
         <v>42214069</v>
       </c>
       <c r="C70" s="1">
-        <v>0</v>
+        <v>12642069</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1154,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="C71" s="1">
-        <v>0</v>
+        <v>20660070</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -1165,7 +1168,7 @@
         <v>47438071</v>
       </c>
       <c r="C72" s="1">
-        <v>0</v>
+        <v>20730071</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1176,7 +1179,7 @@
         <v>52586072</v>
       </c>
       <c r="C73" s="1">
-        <v>0</v>
+        <v>15321072</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -1187,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C74" s="1">
-        <v>0</v>
+        <v>9547073</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -1198,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="C75" s="1">
-        <v>0</v>
+        <v>10391074</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -1209,7 +1212,7 @@
         <v>5982075</v>
       </c>
       <c r="C76" s="1">
-        <v>10964075</v>
+        <v>21444075</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -1220,7 +1223,7 @@
         <v>42253076</v>
       </c>
       <c r="C77" s="1">
-        <v>0</v>
+        <v>15209076</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1228,10 +1231,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="1">
-        <v>44550077</v>
+        <v>0</v>
       </c>
       <c r="C78" s="1">
-        <v>78295077</v>
+        <v>21557077</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -1242,7 +1245,7 @@
         <v>39022078</v>
       </c>
       <c r="C79" s="1">
-        <v>0</v>
+        <v>10278078</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -1253,7 +1256,7 @@
         <v>40792079</v>
       </c>
       <c r="C80" s="1">
-        <v>6847079</v>
+        <v>17311079</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -1264,7 +1267,7 @@
         <v>46057080</v>
       </c>
       <c r="C81" s="1">
-        <v>0</v>
+        <v>16040080</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -1275,7 +1278,7 @@
         <v>43553081</v>
       </c>
       <c r="C82" s="1">
-        <v>8495081</v>
+        <v>20675081</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -1286,7 +1289,7 @@
         <v>40717082</v>
       </c>
       <c r="C83" s="1">
-        <v>3520082</v>
+        <v>13984082</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -1297,7 +1300,7 @@
         <v>39409083</v>
       </c>
       <c r="C84" s="1">
-        <v>0</v>
+        <v>10874083</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -1308,7 +1311,7 @@
         <v>42244084</v>
       </c>
       <c r="C85" s="1">
-        <v>0</v>
+        <v>12704084</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -1319,7 +1322,7 @@
         <v>41869085</v>
       </c>
       <c r="C86" s="1">
-        <v>8489085</v>
+        <v>20615085</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -1327,10 +1330,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="1">
-        <v>41069086</v>
+        <v>0</v>
       </c>
       <c r="C87" s="1">
-        <v>0</v>
+        <v>10890086</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -1341,7 +1344,7 @@
         <v>44119087</v>
       </c>
       <c r="C88" s="1">
-        <v>0</v>
+        <v>10648087</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -1352,7 +1355,7 @@
         <v>44012088</v>
       </c>
       <c r="C89" s="1">
-        <v>9022088</v>
+        <v>21910088</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -1363,7 +1366,7 @@
         <v>42199089</v>
       </c>
       <c r="C90" s="1">
-        <v>13266089</v>
+        <v>25900089</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -1374,7 +1377,7 @@
         <v>44103090</v>
       </c>
       <c r="C91" s="1">
-        <v>0</v>
+        <v>13494090</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -1385,7 +1388,7 @@
         <v>52407091</v>
       </c>
       <c r="C92" s="1">
-        <v>7240091</v>
+        <v>28004091</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -1396,7 +1399,7 @@
         <v>50933092</v>
       </c>
       <c r="C93" s="1">
-        <v>0</v>
+        <v>23562092</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -1407,7 +1410,7 @@
         <v>46048093</v>
       </c>
       <c r="C94" s="1">
-        <v>0</v>
+        <v>16028093</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -1418,7 +1421,7 @@
         <v>39095094</v>
       </c>
       <c r="C95" s="1">
-        <v>7068094</v>
+        <v>17458094</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -1426,10 +1429,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="1">
-        <v>45741095</v>
+        <v>0</v>
       </c>
       <c r="C96" s="1">
-        <v>3725095</v>
+        <v>14205095</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -1440,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="C97" s="1">
-        <v>0</v>
+        <v>15268096</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -1448,10 +1451,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="1">
-        <v>41251097</v>
+        <v>0</v>
       </c>
       <c r="C98" s="1">
-        <v>0</v>
+        <v>16260097</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -1462,7 +1465,7 @@
         <v>39022098</v>
       </c>
       <c r="C99" s="1">
-        <v>0</v>
+        <v>10278098</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -1473,7 +1476,7 @@
         <v>40792099</v>
       </c>
       <c r="C100" s="1">
-        <v>7325099</v>
+        <v>17789099</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -1484,7 +1487,7 @@
         <v>41108100</v>
       </c>
       <c r="C101" s="1">
-        <v>0</v>
+        <v>16040100</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\charges\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13A977C-E047-429D-B485-6B7C3AFF6A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39669BD-2F0B-4EDB-A656-0B88CCBFD8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -450,7 +450,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>18017006</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1">
         <v>18513006</v>
@@ -549,7 +549,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>42451015</v>
+        <v>0</v>
       </c>
       <c r="C16" s="1">
         <v>10480015</v>
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="1">
-        <v>16262017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -648,7 +648,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>40595024</v>
+        <v>0</v>
       </c>
       <c r="C25" s="1">
         <v>21597024</v>
@@ -681,7 +681,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>66637027</v>
+        <v>40919027</v>
       </c>
       <c r="C28" s="1">
         <v>17140027</v>
@@ -725,7 +725,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>50767031</v>
+        <v>0</v>
       </c>
       <c r="C32" s="1">
         <v>20764031</v>
@@ -747,7 +747,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1">
-        <v>46049033</v>
+        <v>0</v>
       </c>
       <c r="C34" s="1">
         <v>15928033</v>
@@ -780,10 +780,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1">
-        <v>43906036</v>
+        <v>0</v>
       </c>
       <c r="C37" s="1">
-        <v>20612036</v>
+        <v>15268036</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -805,7 +805,7 @@
         <v>39022038</v>
       </c>
       <c r="C39" s="1">
-        <v>10279038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -868,7 +868,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1">
-        <v>39892044</v>
+        <v>0</v>
       </c>
       <c r="C45" s="1">
         <v>12584044</v>
@@ -1014,7 +1014,7 @@
         <v>43632057</v>
       </c>
       <c r="C58" s="1">
-        <v>16287057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1132,10 +1132,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="1">
-        <v>42363068</v>
+        <v>0</v>
       </c>
       <c r="C69" s="1">
-        <v>17399068</v>
+        <v>12888068</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1143,10 +1143,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="1">
-        <v>42214069</v>
+        <v>0</v>
       </c>
       <c r="C70" s="1">
-        <v>12642069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1165,7 +1165,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1">
-        <v>47438071</v>
+        <v>0</v>
       </c>
       <c r="C72" s="1">
         <v>20730071</v>
@@ -1220,7 +1220,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="1">
-        <v>42253076</v>
+        <v>0</v>
       </c>
       <c r="C77" s="1">
         <v>15209076</v>
@@ -1264,10 +1264,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="1">
-        <v>46057080</v>
+        <v>0</v>
       </c>
       <c r="C81" s="1">
-        <v>16040080</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -1363,7 +1363,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="1">
-        <v>42199089</v>
+        <v>0</v>
       </c>
       <c r="C90" s="1">
         <v>25900089</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\charges\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39669BD-2F0B-4EDB-A656-0B88CCBFD8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EAC8F9-3D6A-491F-BC46-4A53FC821410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -406,7 +406,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>39132002</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1">
         <v>42196002</v>
@@ -439,7 +439,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>45289005</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -461,7 +461,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>42214007</v>
+        <v>0</v>
       </c>
       <c r="C8" s="1">
         <v>25949007</v>
@@ -472,10 +472,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>75120008</v>
+        <v>0</v>
       </c>
       <c r="C9" s="1">
-        <v>13391008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -596,7 +596,7 @@
         <v>40792019</v>
       </c>
       <c r="C20" s="1">
-        <v>10465019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -615,10 +615,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>40255021</v>
+        <v>0</v>
       </c>
       <c r="C22" s="1">
-        <v>20639021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="1">
-        <v>10892026</v>
+        <v>7081026</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -802,7 +802,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>39022038</v>
+        <v>0</v>
       </c>
       <c r="C39" s="1">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1">
-        <v>40211043</v>
+        <v>0</v>
       </c>
       <c r="C44" s="1">
         <v>10874043</v>
@@ -1000,7 +1000,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1">
-        <v>43820056</v>
+        <v>0</v>
       </c>
       <c r="C57" s="1">
         <v>15253056</v>
@@ -1033,7 +1033,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1">
-        <v>40792059</v>
+        <v>0</v>
       </c>
       <c r="C60" s="1">
         <v>10465059</v>
@@ -1275,7 +1275,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="1">
-        <v>43553081</v>
+        <v>0</v>
       </c>
       <c r="C82" s="1">
         <v>20675081</v>
@@ -1286,7 +1286,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="1">
-        <v>40717082</v>
+        <v>0</v>
       </c>
       <c r="C83" s="1">
         <v>13984082</v>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="C87" s="1">
-        <v>10890086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
